--- a/data/trans_orig/IP2005-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2005-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56793</t>
+          <t>57007</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>64967</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>77584</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>72936</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>80952</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>87,08%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>139457</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>132817</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>144143</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>87,41%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>94,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>77584</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>72900</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>80953</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>87,04%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>139457</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>133065</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>144360</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>87,58%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6172</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2804</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10820</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>12486</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>7800</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>19126</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>5,13%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6172</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2803</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10856</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>12486</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>7583</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>18878</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>224776</t>
+          <t>224218</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>238541</t>
+          <t>238098</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>224133</t>
+          <t>223184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237887</t>
+          <t>237353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>452982</t>
+          <t>452349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>472738</t>
+          <t>472311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>29038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>31038</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50367</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97598</t>
+          <t>97914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111078</t>
+          <t>111161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110232</t>
+          <t>109532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123473</t>
+          <t>123602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>212896</t>
+          <t>213726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231625</t>
+          <t>231533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>29284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>51311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158008</t>
+          <t>157367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172732</t>
+          <t>172488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>167407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182899</t>
+          <t>182962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329499</t>
+          <t>329770</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>352448</t>
+          <t>352087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>33134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41525</t>
+          <t>41886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64474</t>
+          <t>64203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>552531</t>
+          <t>550920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>576424</t>
+          <t>577113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>588262</t>
+          <t>588853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>613949</t>
+          <t>615466</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1148769</t>
+          <t>1147811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1184449</t>
+          <t>1183551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59614</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83507</t>
+          <t>85118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64316</t>
+          <t>62799</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>89412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>129854</t>
+          <t>130752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165534</t>
+          <t>166492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92429</t>
+          <t>91504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98216</t>
+          <t>97981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91433</t>
+          <t>91533</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>184969</t>
+          <t>186177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192944</t>
+          <t>193241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>208523</t>
+          <t>208647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223515</t>
+          <t>223265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244825</t>
+          <t>244729</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>258470</t>
+          <t>258298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>458482</t>
+          <t>458243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>478164</t>
+          <t>477733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27727</t>
+          <t>27603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46759</t>
+          <t>46998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129358</t>
+          <t>129104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142919</t>
+          <t>142547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128951</t>
+          <t>128950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143581</t>
+          <t>143144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263032</t>
+          <t>261568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282277</t>
+          <t>282045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25876</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28464</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30372</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>51081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140033</t>
+          <t>138877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153534</t>
+          <t>153571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143898</t>
+          <t>143075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159071</t>
+          <t>158495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>288075</t>
+          <t>287620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308790</t>
+          <t>308658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>16389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29927</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18193</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33366</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38434</t>
+          <t>38566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59149</t>
+          <t>59604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>582311</t>
+          <t>582533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>608271</t>
+          <t>607939</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>622104</t>
+          <t>622114</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>647771</t>
+          <t>647513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1212613</t>
+          <t>1213770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1249917</t>
+          <t>1248925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78003</t>
+          <t>77781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>52080</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77489</t>
+          <t>77479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>109990</t>
+          <t>110982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>147294</t>
+          <t>146137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85473</t>
+          <t>84736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165193</t>
+          <t>165735</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>191962</t>
+          <t>191992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>203061</t>
+          <t>203374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240730</t>
+          <t>240809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>251462</t>
+          <t>251363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>436591</t>
+          <t>437656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>451920</t>
+          <t>452647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165658</t>
+          <t>165922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177957</t>
+          <t>177654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149453</t>
+          <t>150178</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166209</t>
+          <t>166802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320248</t>
+          <t>320219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340825</t>
+          <t>340904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21019</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37775</t>
+          <t>37050</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53730</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146688</t>
+          <t>146471</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159593</t>
+          <t>159532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141803</t>
+          <t>141540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157514</t>
+          <t>157312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,47 +5706,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>90,75%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>304362</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>293713</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>313761</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>88,15%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>85,06%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>90,87%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>304362</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>293695</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>313645</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>88,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>85,06%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25255</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>16036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>31808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,42 +5819,42 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>40929</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>31530</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>51578</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>11,85%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>9,13%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>40929</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>31646</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>51596</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>600248</t>
+          <t>600600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>621850</t>
+          <t>621485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>622476</t>
+          <t>623220</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>648463</t>
+          <t>648223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1231855</t>
+          <t>1229970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1266165</t>
+          <t>1263683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>55776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49689</t>
+          <t>49929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75676</t>
+          <t>74932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>90844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122672</t>
+          <t>124557</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33854</t>
+          <t>33851</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42543</t>
+          <t>42502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43665</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72518</t>
+          <t>72481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84215</t>
+          <t>84390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24261</t>
+          <t>24298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132181</t>
+          <t>131811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145422</t>
+          <t>145420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>150794</t>
+          <t>151810</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165468</t>
+          <t>165859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287272</t>
+          <t>288027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>308138</t>
+          <t>308129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26955</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>51965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>143163</t>
+          <t>143255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158463</t>
+          <t>158659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171834</t>
+          <t>172588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>191755</t>
+          <t>191671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320028</t>
+          <t>320500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344715</t>
+          <t>344962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>39902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40848</t>
+          <t>40601</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65535</t>
+          <t>65063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>236023</t>
+          <t>235394</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256612</t>
+          <t>256623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>262370</t>
+          <t>263108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>283962</t>
+          <t>284994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>506615</t>
+          <t>506920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>536144</t>
+          <t>535162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21521</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>42375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44796</t>
+          <t>45778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74325</t>
+          <t>74020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>561306</t>
+          <t>561769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>591304</t>
+          <t>591434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638014</t>
+          <t>638033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>673197</t>
+          <t>672062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1209241</t>
+          <t>1212458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1254989</t>
+          <t>1257706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>94747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73562</t>
+          <t>74697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108745</t>
+          <t>108726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148286</t>
+          <t>145569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194034</t>
+          <t>190817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2005-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2005-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2007 (tasa de respuesta: 98,55%)</t>
+          <t>Menores según si sus dientes están sanos en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>77584</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72664</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>80473</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>61874</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>57007</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>64967</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>57597</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>64926</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>90,74%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>83,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>77584</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>72936</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>80952</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132817</t>
+          <t>132827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144143</t>
+          <t>143940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6172</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11092</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6313</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3220</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11180</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3261</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10590</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6172</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2804</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10820</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83756</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83756</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83756</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>68187</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>68187</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>68187</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83756</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83756</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83756</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>231424</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>224016</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>237592</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>88,82%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>232185</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>224218</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>238098</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>224262</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>238004</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>92,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>89,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>231424</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>223184</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>237353</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>452349</t>
+          <t>452413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>472311</t>
+          <t>472870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20798</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14630</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28206</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18943</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13030</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26910</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>26866</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>7,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20798</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14869</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>29038</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31038</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>50936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252222</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252222</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252222</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>376</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>251128</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>251128</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>251128</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252222</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252222</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252222</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>117478</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>110398</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>123855</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>84,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>79,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>105311</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>97914</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>111161</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>97474</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>111382</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>83,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>77,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>88,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>117478</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>109532</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>123602</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>84,63%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213726</t>
+          <t>211646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231533</t>
+          <t>232001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -1527,67 +1527,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>21338</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28418</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>20911</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15061</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28308</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>14840</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>28748</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>16,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21338</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15214</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>29284</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>33036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51311</t>
+          <t>53391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>138816</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>138816</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>138816</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>126222</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>126222</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>126222</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>138816</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>138816</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>138816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>175960</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>168015</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>183594</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>86,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>165673</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>157367</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>172488</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>158073</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>172268</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>86,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>175960</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>167407</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>182962</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>86,48%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329770</t>
+          <t>328642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>352087</t>
+          <t>351676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27512</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19878</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35457</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24828</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18013</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>33134</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>18233</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>32428</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27512</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20510</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>36065</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>13,52%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41886</t>
+          <t>42297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64203</t>
+          <t>65331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203472</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203472</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203472</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>190501</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>190501</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>190501</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203472</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203472</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>588001</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>615775</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>842</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>565042</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>550920</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>577113</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>552078</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>577011</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>88,84%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>602445</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>588853</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>615466</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1147811</t>
+          <t>1151246</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1183551</t>
+          <t>1186030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>75820</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>62490</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>90264</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>70996</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>58925</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>85118</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>59027</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>83960</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>11,16%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>75820</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>62799</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>89412</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>130752</t>
+          <t>128273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>166492</t>
+          <t>163057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>678265</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>678265</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>678265</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>950</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>636038</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>636038</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>636038</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>678265</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>678265</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>678265</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2012 (tasa de respuesta: 99,54%)</t>
+          <t>Menores según si sus dientes están sanos en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>94648</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91961</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>96119</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>91504</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>97981</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>92593</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>98220</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>97,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>94648</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>91533</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186177</t>
+          <t>186443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193241</t>
+          <t>192975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>889</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7366</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6277</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4390</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>252192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>244071</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>258352</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>90,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>217267</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>208647</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>223265</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>208397</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>223920</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>91,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>88,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>252192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>244729</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>258298</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>93,75%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>458243</t>
+          <t>458063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>477733</t>
+          <t>478640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16799</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10639</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24920</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18983</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12985</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27603</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12330</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27853</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>16799</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10693</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>24262</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27508</t>
+          <t>26601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46998</t>
+          <t>47178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>137002</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>129530</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>143328</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>87,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>82,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>136172</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>129104</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>129002</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>142337</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>87,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>137002</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>128950</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>143144</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261568</t>
+          <t>261866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>281853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -3474,67 +3474,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>20413</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14087</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27885</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>19062</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12687</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26130</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12897</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26232</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>12,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20413</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>14271</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>28465</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30604</t>
+          <t>30796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51081</t>
+          <t>50783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157415</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157415</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157415</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155234</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155234</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155234</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157415</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157415</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157415</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>152132</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>144029</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>158749</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>81,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>89,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>146930</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>138877</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>153571</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>138716</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>153393</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>86,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>152132</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>143075</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>158495</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>85,82%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>287620</t>
+          <t>287120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308658</t>
+          <t>308924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25132</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18515</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33235</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23030</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16389</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31083</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16567</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>31244</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>25132</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>18769</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>34189</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>14,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38566</t>
+          <t>38300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59604</t>
+          <t>60104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177264</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177264</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177264</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>169960</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>169960</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>169960</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177264</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177264</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177264</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>635974</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>621627</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>647096</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>861</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>596489</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>582533</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>607939</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>583154</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>609046</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>90,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>635974</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>622114</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>647513</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1213770</t>
+          <t>1213678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1248925</t>
+          <t>1247739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -4160,67 +4160,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>63619</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>52497</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>77966</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>63825</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>52375</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>77781</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>51268</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>77160</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>9,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>63619</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>52080</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>77479</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110982</t>
+          <t>112168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146137</t>
+          <t>146229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699593</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699593</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699593</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>660314</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>660314</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>660314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>699593</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>699593</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>699593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2016 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según si sus dientes están sanos en 2016 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,74 +4617,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>87288</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>84736</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>84602</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>262</t>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165735</t>
+          <t>165208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4730,107 +4730,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>571</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3123</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3257</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2339</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>246914</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>240073</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>251321</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>93,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>198720</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>191992</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>203374</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>192540</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>203567</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>94,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>246914</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>240809</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>251363</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>437656</t>
+          <t>437023</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>452647</t>
+          <t>452362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10447</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17288</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11103</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6449</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17831</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6256</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17283</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>5,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>10447</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5998</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16552</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>30161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>257361</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>257361</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>257361</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>257361</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>257361</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>257361</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>158802</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>149751</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>166664</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>84,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>79,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>172247</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>165922</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>177654</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>165725</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>177784</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>92,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>88,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>158802</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>150178</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>166802</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>84,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320219</t>
+          <t>320625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340904</t>
+          <t>340431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28426</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20564</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37477</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>14503</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9096</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20828</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8966</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>21025</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>7,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>28426</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20426</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37050</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>33547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>53353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>186750</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>186750</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>186750</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>150681</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>141501</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>157371</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>81,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>153681</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>146471</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>159532</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>145843</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>159243</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>89,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>85,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>150681</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>141540</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>157312</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>86,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293713</t>
+          <t>293454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313761</t>
+          <t>313292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22667</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15977</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31847</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18262</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12411</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25472</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12700</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26100</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,62%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>22667</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>16036</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>31808</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31530</t>
+          <t>31999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51578</t>
+          <t>51837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173348</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173348</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173348</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171943</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171943</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171943</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173348</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173348</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173348</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>623795</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>648383</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>918</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>611937</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>600600</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>621485</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>599300</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>621013</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>93,23%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>636612</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>623220</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>648223</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1229970</t>
+          <t>1231256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1263683</t>
+          <t>1264212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61540</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>49769</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>74357</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>44439</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>34891</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>55776</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>35363</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>57076</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>61540</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>49929</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>74932</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90844</t>
+          <t>90315</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124557</t>
+          <t>123271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>698152</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>698152</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>698152</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>656376</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>656376</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>656376</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>698152</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>698152</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>698152</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si sus dientes están sanos en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33389</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29907</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36131</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>38701</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>33851</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42502</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>79,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>69,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40528</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36253</t>
+          <t>31061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44022</t>
+          <t>39248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>79229</t>
+          <t>68833</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72481</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84390</t>
+          <t>73363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6287</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9769</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10149</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6348</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14999</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20,78%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>48850</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>48850</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48850</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>96779</t>
+          <t>84598</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96779</t>
+          <t>84598</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96779</t>
+          <t>84598</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>137425</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>130290</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>143383</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>88,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>139273</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>131811</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>145420</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>82,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>159411</t>
+          <t>126159</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>151810</t>
+          <t>118749</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165859</t>
+          <t>131084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>298683</t>
+          <t>263585</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288027</t>
+          <t>254532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>308129</t>
+          <t>271954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18702</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12744</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25837</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19863</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13716</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27325</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29047</t>
+          <t>26276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>37568</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31863</t>
+          <t>29199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51965</t>
+          <t>46621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156127</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156127</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156127</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>180857</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>180857</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>180857</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>339992</t>
+          <t>301153</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>339992</t>
+          <t>301153</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>339992</t>
+          <t>301153</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>171202</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>161635</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>179667</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>80,77%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>151614</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>143255</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>158659</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>87,6%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>182336</t>
+          <t>152099</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172588</t>
+          <t>142795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>191671</t>
+          <t>159275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>333951</t>
+          <t>323301</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320500</t>
+          <t>311985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344962</t>
+          <t>335894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28924</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20459</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38491</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21458</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14413</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29817</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30154</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39902</t>
+          <t>31877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>51612</t>
+          <t>51497</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>38904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65063</t>
+          <t>62813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>263440</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>251172</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>272591</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>85,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>246964</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>235394</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>256623</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>85,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>93,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>274816</t>
+          <t>227884</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263108</t>
+          <t>217746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>284994</t>
+          <t>235530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>521779</t>
+          <t>491324</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>506920</t>
+          <t>477414</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>535162</t>
+          <t>503653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29205</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20054</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41473</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>28494</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18835</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>40064</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>28669</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>59161</t>
+          <t>57874</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45778</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74020</t>
+          <t>71784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>605456</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>588897</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>619965</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>85,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>804</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>576551</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>561769</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>591434</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>87,82%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>85,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>657092</t>
+          <t>541586</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638033</t>
+          <t>526008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>672062</t>
+          <t>553879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1233643</t>
+          <t>1147041</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1212458</t>
+          <t>1125379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1257706</t>
+          <t>1165551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>83118</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68609</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>99677</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>79965</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>65082</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>94747</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>79587</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74697</t>
+          <t>67294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108726</t>
+          <t>95165</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>169632</t>
+          <t>162705</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145569</t>
+          <t>144195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190817</t>
+          <t>184367</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>688574</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>688574</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>688574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>922</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>656516</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>656516</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>656516</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>746759</t>
+          <t>621173</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>746759</t>
+          <t>621173</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>746759</t>
+          <t>621173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1403275</t>
+          <t>1309746</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1403275</t>
+          <t>1309746</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1403275</t>
+          <t>1309746</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
